--- a/hardware/采购清单.xlsx
+++ b/hardware/采购清单.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="283">
   <si>
     <t xml:space="preserve">板卡数量</t>
   </si>
@@ -28,10 +28,10 @@
     <t xml:space="preserve">无需采购</t>
   </si>
   <si>
-    <t xml:space="preserve">已有</t>
-  </si>
-  <si>
-    <t xml:space="preserve">需要采购</t>
+    <t xml:space="preserve">建议嘉立创采购</t>
+  </si>
+  <si>
+    <t xml:space="preserve">建议淘宝采购</t>
   </si>
   <si>
     <t xml:space="preserve">Reference</t>
@@ -460,7 +460,7 @@
     <t xml:space="preserve">10k</t>
   </si>
   <si>
-    <t xml:space="preserve">R12,R13,R44,R45,R46</t>
+    <t xml:space="preserve">R12,R13,R44,R45,R46,R49,R51,R53</t>
   </si>
   <si>
     <t xml:space="preserve">C3152168</t>
@@ -473,15 +473,6 @@
   </si>
   <si>
     <t xml:space="preserve">C22369939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R49,R51,R53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C862232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5k</t>
   </si>
   <si>
     <t xml:space="preserve">R54,R55,R56</t>
@@ -1162,7 +1153,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Noto Sans CJK TC"/>
@@ -1189,11 +1180,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1262,7 +1248,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1296,10 +1282,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1388,7 +1370,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.24"/>
@@ -1468,171 +1450,171 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+    <row r="4" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <f aca="false">B1*G4</f>
         <v>10</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="5" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+    <row r="5" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <f aca="false">B1*G5</f>
         <v>5</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="8" t="s">
+      <c r="E5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" s="5" customFormat="true" ht="43.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" s="4" customFormat="true" ht="43.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <f aca="false">B1*G6</f>
         <v>30</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="8" t="s">
+      <c r="E6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="7" s="5" customFormat="true" ht="138.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+    <row r="7" s="4" customFormat="true" ht="138.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
         <f aca="false">B1*G7</f>
         <v>230</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="8" t="s">
+      <c r="E7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="4" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="8" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+    <row r="8" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <f aca="false">B1*G8</f>
         <v>15</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="E8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="9" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+    <row r="9" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="4" t="n">
         <f aca="false">B1*G9</f>
         <v>5</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="E9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="G9" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="4" t="n">
         <f aca="false">B1*G10</f>
         <v>10</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="8" t="s">
+      <c r="E10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1660,27 +1642,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+    <row r="12" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="4" t="n">
         <f aca="false">B1*G12</f>
         <v>5</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="8" t="s">
+      <c r="E12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1780,603 +1762,603 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" s="5" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
+    <row r="17" s="4" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="4" t="n">
         <f aca="false">B1*G17</f>
         <v>45</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="4" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="18" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+    <row r="18" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="5" t="n">
         <f aca="false">B1*G18</f>
         <v>5</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="7" t="s">
+      <c r="E18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G18" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" s="4" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="G18" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" s="5" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="5" t="n">
         <f aca="false">B1*G19</f>
         <v>5</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="7" t="s">
+      <c r="E19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G19" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="G19" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="5" t="n">
         <f aca="false">B1*G20</f>
         <v>5</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="7" t="s">
+      <c r="E20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G20" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="G20" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="5" t="n">
         <f aca="false">B1*G21</f>
         <v>5</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="7" t="s">
+      <c r="E21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="G21" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" s="4" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="G21" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" s="5" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="5" t="n">
         <f aca="false">B1*G22</f>
         <v>5</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="7" t="s">
+      <c r="E22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G22" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" s="4" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
+      <c r="G22" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" s="5" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="5" t="n">
         <f aca="false">B1*G23</f>
         <v>5</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="7" t="s">
+      <c r="E23" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G23" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" s="4" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
+      <c r="G23" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" s="5" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="5" t="n">
         <f aca="false">B1*G24</f>
         <v>5</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="7" t="s">
+      <c r="E24" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G24" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" s="4" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
+      <c r="G24" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" s="5" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="5" t="n">
         <f aca="false">B1*G25</f>
         <v>5</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="7" t="s">
+      <c r="E25" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="G25" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
+      <c r="G25" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="5" t="n">
         <f aca="false">B1*G26</f>
         <v>5</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" s="7" t="s">
+      <c r="E26" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="G26" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
+      <c r="G26" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="C27" s="5" t="n">
         <f aca="false">B1*G27</f>
         <v>5</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" s="7" t="s">
+      <c r="E27" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="G27" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
+      <c r="G27" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="5" t="n">
         <f aca="false">B1*G28</f>
         <v>5</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" s="7" t="s">
+      <c r="E28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="G28" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
+      <c r="G28" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" s="5" t="n">
         <f aca="false">B1*G29</f>
         <v>5</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" s="7" t="s">
+      <c r="E29" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
+      <c r="G29" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="5" t="n">
         <f aca="false">B1*G30</f>
         <v>5</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" s="7" t="s">
+      <c r="E30" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G30" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="s">
+      <c r="G30" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="5" t="n">
         <f aca="false">B1*G31</f>
         <v>5</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31" s="7" t="s">
+      <c r="E31" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G31" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="s">
+      <c r="G31" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="5" t="n">
         <f aca="false">B1*G32</f>
         <v>5</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" s="7" t="s">
+      <c r="E32" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G32" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
+      <c r="G32" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="5" t="n">
         <f aca="false">B1*G33</f>
         <v>5</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33" s="7" t="s">
+      <c r="E33" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="G33" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="s">
+      <c r="G33" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="5" t="n">
         <f aca="false">B1*G34</f>
         <v>5</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F34" s="7" t="s">
+      <c r="E34" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="G34" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="s">
+      <c r="G34" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C35" s="5" t="n">
         <f aca="false">B1*G35</f>
         <v>5</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" s="7" t="s">
+      <c r="E35" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="G35" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="s">
+      <c r="G35" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="4" t="n">
         <f aca="false">B1*G36</f>
         <v>5</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E36" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="8" t="s">
+      <c r="E36" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="G36" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8" t="s">
+      <c r="G36" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" s="4" t="n">
         <f aca="false">B1*G37</f>
         <v>5</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E37" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37" s="8" t="s">
+      <c r="E37" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="G37" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="s">
+      <c r="G37" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" s="4" t="n">
         <f aca="false">B1*G38</f>
         <v>5</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="E38" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F38" s="8" t="s">
+      <c r="E38" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="G38" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8" t="s">
+      <c r="G38" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C39" s="4" t="n">
         <f aca="false">B1*G39</f>
         <v>5</v>
       </c>
-      <c r="D39" s="5" t="n">
+      <c r="D39" s="4" t="n">
         <v>330</v>
       </c>
-      <c r="E39" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" s="8" t="s">
+      <c r="E39" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="G39" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" s="5" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
+      <c r="G39" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" s="4" customFormat="true" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C40" s="4" t="n">
         <f aca="false">B1*G40</f>
         <v>55</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E40" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F40" s="8" t="s">
+      <c r="E40" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="G40" s="5" t="n">
+      <c r="G40" s="4" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="41" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
+    <row r="41" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C41" s="4" t="n">
         <f aca="false">B1*G41</f>
         <v>5</v>
       </c>
-      <c r="D41" s="5" t="n">
+      <c r="D41" s="4" t="n">
         <v>0.22</v>
       </c>
-      <c r="E41" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F41" s="8" t="s">
+      <c r="E41" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="G41" s="5" t="n">
+      <c r="G41" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2404,107 +2386,107 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" s="5" customFormat="true" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8" t="s">
+    <row r="43" s="4" customFormat="true" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C43" s="4" t="n">
         <f aca="false">B1*G43</f>
         <v>165</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E43" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F43" s="8" t="s">
+      <c r="E43" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="G43" s="5" t="n">
+      <c r="G43" s="4" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="44" s="5" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
+    <row r="44" s="4" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C44" s="4" t="n">
         <f aca="false">B1*G44</f>
-        <v>25</v>
-      </c>
-      <c r="D44" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E44" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F44" s="8" t="s">
+      <c r="E44" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="G44" s="5" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9" t="s">
+      <c r="G44" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C45" s="4" t="n">
         <f aca="false">B1*G45</f>
         <v>15</v>
       </c>
-      <c r="D45" s="5" t="n">
+      <c r="D45" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="E45" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F45" s="8" t="s">
+      <c r="E45" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F45" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="G45" s="5" t="n">
+      <c r="G45" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="46" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8" t="s">
+    <row r="46" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="5" t="n">
+      <c r="C46" s="4" t="n">
         <f aca="false">B1*G46</f>
         <v>15</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="E46" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F46" s="8" t="s">
+      <c r="E46" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="G46" s="5" t="n">
+      <c r="G46" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="47" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="5" t="s">
         <v>155</v>
       </c>
       <c r="C47" s="5" t="n">
@@ -2518,7 +2500,7 @@
         <v>15</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="G47" s="5" t="n">
         <v>3</v>
@@ -2526,23 +2508,23 @@
     </row>
     <row r="48" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C48" s="5" t="n">
         <f aca="false">B1*G48</f>
         <v>15</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>3</v>
@@ -2557,7 +2539,7 @@
       </c>
       <c r="C49" s="5" t="n">
         <f aca="false">B1*G49</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>163</v>
@@ -2566,134 +2548,134 @@
         <v>15</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B50" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" s="5" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C50" s="4" t="n">
+      <c r="B50" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C50" s="5" t="n">
         <f aca="false">B1*G50</f>
         <v>5</v>
       </c>
-      <c r="D50" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F50" s="7" t="s">
+      <c r="D50" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="G50" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" s="4" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="s">
+      <c r="E50" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="G50" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" s="5" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C51" s="4" t="n">
+      <c r="B51" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C51" s="5" t="n">
         <f aca="false">B1*G51</f>
         <v>5</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" s="5" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <f aca="false">B1*G52</f>
+        <v>5</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" s="5" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E51" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" s="4" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="s">
+      <c r="C53" s="5" t="n">
+        <f aca="false">B1*G53</f>
+        <v>5</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F53" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="B52" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <f aca="false">B1*G52</f>
-        <v>5</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" s="4" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <f aca="false">B1*G53</f>
-        <v>5</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F53" s="7" t="s">
+      <c r="G53" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="G53" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" s="4" customFormat="true" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
+      <c r="B54" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <f aca="false">B1*G54</f>
+        <v>5</v>
+      </c>
+      <c r="D54" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <f aca="false">B1*G54</f>
-        <v>5</v>
-      </c>
-      <c r="D54" s="7" t="s">
+      <c r="E54" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="E54" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="55" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="9" t="s">
         <v>182</v>
       </c>
       <c r="B55" s="3" t="s">
@@ -2703,22 +2685,22 @@
         <f aca="false">B1*G55</f>
         <v>5</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="E55" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F55" s="10" t="s">
+      <c r="E55" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="9" t="s">
         <v>184</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>1</v>
@@ -2727,22 +2709,22 @@
         <f aca="false">B1*G56</f>
         <v>5</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="D56" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="9" t="s">
         <v>186</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F56" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>1</v>
@@ -2751,22 +2733,22 @@
         <f aca="false">B1*G57</f>
         <v>5</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="D57" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>1</v>
@@ -2775,22 +2757,22 @@
         <f aca="false">B1*G58</f>
         <v>5</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="D58" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F58" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>1</v>
@@ -2799,22 +2781,22 @@
         <f aca="false">B1*G59</f>
         <v>5</v>
       </c>
-      <c r="D59" s="10" t="s">
+      <c r="D59" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="9" t="s">
         <v>192</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="G59" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>1</v>
@@ -2823,22 +2805,22 @@
         <f aca="false">B1*G60</f>
         <v>5</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D60" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="9" t="s">
         <v>194</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F60" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>1</v>
@@ -2847,22 +2829,22 @@
         <f aca="false">B1*G61</f>
         <v>5</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="D61" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="9" t="s">
         <v>196</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>1</v>
@@ -2871,22 +2853,22 @@
         <f aca="false">B1*G62</f>
         <v>5</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="D62" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F62" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>1</v>
@@ -2895,472 +2877,448 @@
         <f aca="false">B1*G63</f>
         <v>5</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="D63" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="E63" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F63" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="10" t="s">
+      <c r="B64" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="10" t="n">
+        <f aca="false">B1*G64</f>
+        <v>5</v>
+      </c>
+      <c r="D64" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C64" s="3" t="n">
-        <f aca="false">B1*G64</f>
-        <v>5</v>
-      </c>
-      <c r="D64" s="10" t="s">
+      <c r="E64" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" s="5" customFormat="true" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="E64" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" s="3" customFormat="true" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="10" t="s">
+      <c r="B65" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C65" s="11" t="n">
+      <c r="C65" s="5" t="n">
         <f aca="false">B1*G65</f>
         <v>5</v>
       </c>
-      <c r="D65" s="10" t="s">
+      <c r="D65" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="E65" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F65" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="G65" s="3" t="n">
+      <c r="E65" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="G65" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="66" s="5" customFormat="true" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C66" s="5" t="n">
         <f aca="false">B1*G66</f>
         <v>5</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G66" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="67" s="5" customFormat="true" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" s="5" customFormat="true" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C67" s="5" t="n">
         <f aca="false">B1*G67</f>
         <v>5</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G67" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="68" s="5" customFormat="true" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" s="5" customFormat="true" ht="58.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C68" s="5" t="n">
         <f aca="false">B1*G68</f>
         <v>5</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G68" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="69" s="5" customFormat="true" ht="58.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" s="5" customFormat="true" ht="70" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C69" s="5" t="n">
         <f aca="false">B1*G69</f>
         <v>5</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G69" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="70" s="4" customFormat="true" ht="70" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="B70" s="4" t="s">
+    <row r="70" s="5" customFormat="true" ht="138.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="C70" s="4" t="n">
+      <c r="B70" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C70" s="5" t="n">
         <f aca="false">B1*G70</f>
         <v>5</v>
       </c>
-      <c r="D70" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="E70" s="7" t="s">
+      <c r="D70" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="F70" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="G70" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" s="5" customFormat="true" ht="138.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E70" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" s="5" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C71" s="5" t="n">
         <f aca="false">B1*G71</f>
         <v>5</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="G71" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="72" s="4" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="C72" s="4" t="n">
+    <row r="72" s="5" customFormat="true" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C72" s="5" t="n">
         <f aca="false">B1*G72</f>
         <v>5</v>
       </c>
-      <c r="D72" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="F72" s="7" t="s">
+      <c r="D72" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="G72" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" s="4" customFormat="true" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="s">
+      <c r="E72" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="F72" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="C73" s="4" t="n">
+      <c r="G72" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" s="5" customFormat="true" ht="47.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C73" s="5" t="n">
         <f aca="false">B1*G73</f>
         <v>5</v>
       </c>
-      <c r="D73" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="F73" s="7" t="s">
+      <c r="D73" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="G73" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" s="4" customFormat="true" ht="47.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7" t="s">
+      <c r="E73" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="F73" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="C74" s="4" t="n">
+      <c r="G73" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" s="5" customFormat="true" ht="70" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C74" s="5" t="n">
         <f aca="false">B1*G74</f>
         <v>5</v>
       </c>
-      <c r="D74" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="F74" s="7" t="s">
+      <c r="D74" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="G74" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" s="5" customFormat="true" ht="70" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E74" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" s="5" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C75" s="5" t="n">
         <f aca="false">B1*G75</f>
         <v>5</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="G75" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="76" s="4" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C76" s="4" t="n">
+    <row r="76" s="5" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C76" s="5" t="n">
         <f aca="false">B1*G76</f>
         <v>5</v>
       </c>
-      <c r="D76" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="F76" s="7" t="s">
+      <c r="D76" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="G76" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" s="4" customFormat="true" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="s">
+      <c r="E76" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="F76" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="C77" s="4" t="n">
+      <c r="G76" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" s="5" customFormat="true" ht="104.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C77" s="5" t="n">
         <f aca="false">B1*G77</f>
-        <v>5</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="F77" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D77" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="G77" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" s="4" customFormat="true" ht="104.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="s">
+      <c r="E77" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="F77" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="C78" s="4" t="n">
+      <c r="G77" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" s="5" customFormat="true" ht="70" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C78" s="5" t="n">
         <f aca="false">B1*G78</f>
-        <v>45</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="F78" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="G78" s="4" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" s="5" customFormat="true" ht="70" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E78" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" s="5" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C79" s="5" t="n">
         <f aca="false">B1*G79</f>
         <v>5</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G79" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="80" s="4" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="C80" s="4" t="n">
+    <row r="80" s="5" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C80" s="5" t="n">
         <f aca="false">B1*G80</f>
         <v>5</v>
       </c>
-      <c r="D80" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="F80" s="7" t="s">
+      <c r="D80" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="G80" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" s="4" customFormat="true" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E80" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>280</v>
       </c>
       <c r="C81" s="4" t="n">
         <f aca="false">B1*G81</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>280</v>
+        <v>15</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="C82" s="4" t="n">
-        <f aca="false">B1*G82</f>
-        <v>10</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="G82" s="4" t="n">
         <v>2</v>
       </c>
     </row>
